--- a/球員中英文對照（更新）.xlsx
+++ b/球員中英文對照（更新）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Desktop/NTU/灼見/python-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286864A1-D8A2-3843-BD2A-1CC08F5774C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE94E21F-2396-3546-9EDD-75C59399FB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="11720" windowHeight="13780" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="373">
   <si>
     <t>球員中文名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1693,6 +1693,26 @@
   </si>
   <si>
     <t>Shay Whitcomb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>國家</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>捷克</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>澳洲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>韓國</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2142,6 +2162,9 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="2" spans="1:3" ht="21.5" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2150,8 +2173,8 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
+      <c r="C2" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.5" customHeight="1">
@@ -2161,8 +2184,8 @@
       <c r="B3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="2">
-        <v>2</v>
+      <c r="C3" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21.5" customHeight="1">
@@ -2172,8 +2195,8 @@
       <c r="B4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="2">
-        <v>3</v>
+      <c r="C4" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.5" customHeight="1">
@@ -2183,8 +2206,8 @@
       <c r="B5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="2">
-        <v>4</v>
+      <c r="C5" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21.5" customHeight="1">
@@ -2194,8 +2217,8 @@
       <c r="B6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="2">
-        <v>5</v>
+      <c r="C6" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21.5" customHeight="1">
@@ -2205,8 +2228,8 @@
       <c r="B7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="2">
-        <v>6</v>
+      <c r="C7" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21.5" customHeight="1">
@@ -2216,8 +2239,8 @@
       <c r="B8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="2">
-        <v>7</v>
+      <c r="C8" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21.5" customHeight="1">
@@ -2227,8 +2250,8 @@
       <c r="B9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="2">
-        <v>8</v>
+      <c r="C9" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21.5" customHeight="1">
@@ -2238,8 +2261,8 @@
       <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="2">
-        <v>12</v>
+      <c r="C10" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21.5" customHeight="1">
@@ -2249,8 +2272,8 @@
       <c r="B11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="2">
-        <v>13</v>
+      <c r="C11" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="21.5" customHeight="1">
@@ -2260,8 +2283,8 @@
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="2">
-        <v>14</v>
+      <c r="C12" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="21.5" customHeight="1">
@@ -2271,8 +2294,8 @@
       <c r="B13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="2">
-        <v>15</v>
+      <c r="C13" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="21.5" customHeight="1">
@@ -2282,8 +2305,8 @@
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2">
-        <v>16</v>
+      <c r="C14" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="21.5" customHeight="1">
@@ -2293,8 +2316,8 @@
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="2">
-        <v>17</v>
+      <c r="C15" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="21.5" customHeight="1">
@@ -2304,8 +2327,8 @@
       <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="2">
-        <v>18</v>
+      <c r="C16" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="21.5" customHeight="1">
@@ -2315,8 +2338,8 @@
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="2">
-        <v>19</v>
+      <c r="C17" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="21.5" customHeight="1">
@@ -2326,8 +2349,8 @@
       <c r="B18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="2">
-        <v>20</v>
+      <c r="C18" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="21.5" customHeight="1">
@@ -2337,8 +2360,8 @@
       <c r="B19" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="2">
-        <v>23</v>
+      <c r="C19" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="21.5" customHeight="1">
@@ -2348,8 +2371,8 @@
       <c r="B20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="2">
-        <v>25</v>
+      <c r="C20" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="21.5" customHeight="1">
@@ -2359,8 +2382,8 @@
       <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="2">
-        <v>26</v>
+      <c r="C21" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="21.5" customHeight="1">
@@ -2370,8 +2393,8 @@
       <c r="B22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="2">
-        <v>27</v>
+      <c r="C22" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="21.5" customHeight="1">
@@ -2381,8 +2404,8 @@
       <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="2">
-        <v>28</v>
+      <c r="C23" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="21.5" customHeight="1">
@@ -2392,8 +2415,8 @@
       <c r="B24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="2">
-        <v>34</v>
+      <c r="C24" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="21.5" customHeight="1">
@@ -2403,8 +2426,8 @@
       <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="2">
-        <v>47</v>
+      <c r="C25" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="21.5" customHeight="1">
@@ -2414,8 +2437,8 @@
       <c r="B26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="2">
-        <v>51</v>
+      <c r="C26" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="21.5" customHeight="1">
@@ -2425,8 +2448,8 @@
       <c r="B27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="2">
-        <v>55</v>
+      <c r="C27" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="21.5" customHeight="1">
@@ -2436,8 +2459,8 @@
       <c r="B28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="2">
-        <v>57</v>
+      <c r="C28" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="21.5" customHeight="1">
@@ -2447,8 +2470,8 @@
       <c r="B29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="2">
-        <v>61</v>
+      <c r="C29" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="21.5" customHeight="1">
@@ -2458,8 +2481,8 @@
       <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="2">
-        <v>66</v>
+      <c r="C30" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="21.5" customHeight="1">
@@ -2469,8 +2492,8 @@
       <c r="B31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="2">
-        <v>69</v>
+      <c r="C31" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="21.5" customHeight="1">
@@ -2480,1221 +2503,1680 @@
       <c r="B32" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C32" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="21.5" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C33" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="21.5" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C34" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="21.5" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C35" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="21.5" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C36" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="21.5" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C37" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="21.5" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C38" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="21.5" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C39" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="21.5" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C40" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="21.5" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C41" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="21.5" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C42" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="21.5" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C43" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="21.5" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C44" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="21.5" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C45" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="21.5" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C46" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="21.5" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C47" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="21.5" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C48" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="21.5" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C49" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="21.5" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C50" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="21.5" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C51" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="21.5" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C52" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="21.5" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C53" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="21.5" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C54" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="21.5" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>108</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C55" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="21.5" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C56" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="21.5" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C57" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="21.5" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C58" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="21.5" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>116</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C59" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="21.5" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C60" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="21.5" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C61" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="21.5" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C62" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="21.5" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C63" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="21.5" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C64" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="21.5" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>128</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C65" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="21.5" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C66" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="21.5" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C67" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="21.5" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C68" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="21.5" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C69" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="21.5" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C70" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="21.5" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>140</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C71" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="21.5" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C72" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="21.5" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C73" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="21.5" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C74" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="21.5" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C75" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="21.5" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C76" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="21.5" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>152</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C77" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="21.5" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C78" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="21.5" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C79" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="21.5" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C80" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="21.5" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>160</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C81" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="21.5" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C82" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="21.5" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>164</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C83" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="21.5" customHeight="1">
       <c r="A84" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C84" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="21.5" customHeight="1">
       <c r="A85" s="1" t="s">
         <v>168</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C85" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="21.5" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C86" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="21.5" customHeight="1">
       <c r="A87" s="1" t="s">
         <v>172</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C87" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="21.5" customHeight="1">
       <c r="A88" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C88" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="21.5" customHeight="1">
       <c r="A89" s="1" t="s">
         <v>176</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C89" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="21.5" customHeight="1">
       <c r="A90" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C90" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="21.5" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>180</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C91" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="21.5" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>182</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C92" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="21.5" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>184</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C93" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="21.5" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>186</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C94" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="21.5" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>188</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C95" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="21.5" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>190</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C96" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="21.5" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C97" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="21.5" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C98" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="21.5" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>196</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C99" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="21.5" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>198</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C100" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="21.5" customHeight="1">
       <c r="A101" s="4" t="s">
         <v>200</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C101" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="21.5" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>202</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C102" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="21.5" customHeight="1">
       <c r="A103" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C103" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="21.5" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C104" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="21.5" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>208</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C105" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="21.5" customHeight="1">
       <c r="A106" s="1" t="s">
         <v>210</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C106" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="21.5" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C107" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="21.5" customHeight="1">
       <c r="A108" s="1" t="s">
         <v>214</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C108" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="21.5" customHeight="1">
       <c r="A109" s="1" t="s">
         <v>216</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C109" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="21.5" customHeight="1">
       <c r="A110" s="1" t="s">
         <v>218</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C110" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="21.5" customHeight="1">
       <c r="A111" s="1" t="s">
         <v>220</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C111" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="21.5" customHeight="1">
       <c r="A112" s="1" t="s">
         <v>222</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C112" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="21.5" customHeight="1">
       <c r="A113" s="1" t="s">
         <v>224</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C113" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="21.5" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C114" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="21.5" customHeight="1">
       <c r="A115" s="1" t="s">
         <v>228</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C115" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="21.5" customHeight="1">
       <c r="A116" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C116" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="21.5" customHeight="1">
       <c r="A117" s="1" t="s">
         <v>232</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C117" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="21.5" customHeight="1">
       <c r="A118" s="1" t="s">
         <v>234</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C118" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="21.5" customHeight="1">
       <c r="A119" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C119" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="21.5" customHeight="1">
       <c r="A120" s="1" t="s">
         <v>238</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C120" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="21.5" customHeight="1">
       <c r="A121" s="1" t="s">
         <v>240</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C121" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="21.5" customHeight="1">
       <c r="A122" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C122" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="21.5" customHeight="1">
       <c r="A123" s="1" t="s">
         <v>244</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C123" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="21.5" customHeight="1">
       <c r="A124" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C124" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="21.5" customHeight="1">
       <c r="A125" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C125" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="21.5" customHeight="1">
       <c r="A126" s="1" t="s">
         <v>250</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C126" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="21.5" customHeight="1">
       <c r="A127" s="1" t="s">
         <v>252</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C127" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="21.5" customHeight="1">
       <c r="A128" s="1" t="s">
         <v>254</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C128" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="21.5" customHeight="1">
       <c r="A129" s="1" t="s">
         <v>256</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C129" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="21.5" customHeight="1">
       <c r="A130" s="1" t="s">
         <v>258</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C130" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="21.5" customHeight="1">
       <c r="A131" s="1" t="s">
         <v>260</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C131" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="21.5" customHeight="1">
       <c r="A132" s="1" t="s">
         <v>262</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C132" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="21.5" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C133" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="21.5" customHeight="1">
       <c r="A134" s="1" t="s">
         <v>266</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C134" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="21.5" customHeight="1">
       <c r="A135" s="1" t="s">
         <v>268</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C135" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="21.5" customHeight="1">
       <c r="A136" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C136" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="21.5" customHeight="1">
       <c r="A137" s="1" t="s">
         <v>272</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C137" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="21.5" customHeight="1">
       <c r="A138" s="1" t="s">
         <v>274</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C138" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="21.5" customHeight="1">
       <c r="A139" s="1" t="s">
         <v>276</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C139" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="21.5" customHeight="1">
       <c r="A140" s="1" t="s">
         <v>278</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C140" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="21.5" customHeight="1">
       <c r="A141" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C141" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="21.5" customHeight="1">
       <c r="A142" s="1" t="s">
         <v>282</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C142" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="21.5" customHeight="1">
       <c r="A143" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C143" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="21.5" customHeight="1">
       <c r="A144" s="1" t="s">
         <v>286</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C144" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="21.5" customHeight="1">
       <c r="A145" s="1" t="s">
         <v>288</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C145" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="21.5" customHeight="1">
       <c r="A146" s="6" t="s">
         <v>290</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C146" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="21.5" customHeight="1">
       <c r="A147" s="6" t="s">
         <v>292</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C147" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="21.5" customHeight="1">
       <c r="A148" s="6" t="s">
         <v>294</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C148" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="21.5" customHeight="1">
       <c r="A149" s="6" t="s">
         <v>296</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C149" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="21.5" customHeight="1">
       <c r="A150" s="6" t="s">
         <v>298</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C150" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="21.5" customHeight="1">
       <c r="A151" s="6" t="s">
         <v>300</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C151" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="21.5" customHeight="1">
       <c r="A152" s="6" t="s">
         <v>302</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C152" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="21.5" customHeight="1">
       <c r="A153" s="6" t="s">
         <v>304</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C153" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="21.5" customHeight="1">
       <c r="A154" s="6" t="s">
         <v>306</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C154" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="21.5" customHeight="1">
       <c r="A155" s="6" t="s">
         <v>308</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C155" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="21.5" customHeight="1">
       <c r="A156" s="6" t="s">
         <v>310</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C156" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="21.5" customHeight="1">
       <c r="A157" s="1" t="s">
         <v>312</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C157" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="21.5" customHeight="1">
       <c r="A158" s="6" t="s">
         <v>314</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C158" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="21.5" customHeight="1">
       <c r="A159" s="6" t="s">
         <v>316</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C159" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="21.5" customHeight="1">
       <c r="A160" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C160" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="21.5" customHeight="1">
       <c r="A161" s="6" t="s">
         <v>320</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C161" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="21.5" customHeight="1">
       <c r="A162" s="6" t="s">
         <v>322</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C162" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="21.5" customHeight="1">
       <c r="A163" s="6" t="s">
         <v>324</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C163" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="21.5" customHeight="1">
       <c r="A164" s="6" t="s">
         <v>326</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C164" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="21.5" customHeight="1">
       <c r="A165" s="6" t="s">
         <v>328</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C165" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="21.5" customHeight="1">
       <c r="A166" s="6" t="s">
         <v>330</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C166" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="21.5" customHeight="1">
       <c r="A167" s="6" t="s">
         <v>332</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C167" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="21.5" customHeight="1">
       <c r="A168" s="6" t="s">
         <v>334</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C168" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="21.5" customHeight="1">
       <c r="A169" s="6" t="s">
         <v>336</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C169" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="21.5" customHeight="1">
       <c r="A170" s="6" t="s">
         <v>338</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C170" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="21.5" customHeight="1">
       <c r="A171" s="6" t="s">
         <v>340</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C171" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="21.5" customHeight="1">
       <c r="A172" s="6" t="s">
         <v>342</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="173" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C172" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="21.5" customHeight="1">
       <c r="A173" s="6" t="s">
         <v>344</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C173" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="21.5" customHeight="1">
       <c r="A174" s="6" t="s">
         <v>346</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C174" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="21.5" customHeight="1">
       <c r="A175" s="6" t="s">
         <v>348</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C175" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="21.5" customHeight="1">
       <c r="A176" s="6" t="s">
         <v>350</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C176" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="21.5" customHeight="1">
       <c r="A177" s="6" t="s">
         <v>352</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C177" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="21.5" customHeight="1">
       <c r="A178" s="6" t="s">
         <v>354</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C178" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="21.5" customHeight="1">
       <c r="A179" s="6" t="s">
         <v>356</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C179" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="21.5" customHeight="1">
       <c r="A180" s="6" t="s">
         <v>358</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C180" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="21.5" customHeight="1">
       <c r="A181" s="1" t="s">
         <v>360</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C181" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="21.5" customHeight="1">
       <c r="A182" s="1" t="s">
         <v>362</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C182" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="21.5" customHeight="1">
       <c r="A183" s="1" t="s">
         <v>364</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C183" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="21.5" customHeight="1">
       <c r="A184" s="1" t="s">
         <v>366</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>367</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/球員中英文對照（更新）.xlsx
+++ b/球員中英文對照（更新）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Desktop/NTU/灼見/python-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE94E21F-2396-3546-9EDD-75C59399FB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412897FD-D14C-F844-9B91-6B500FE82241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="431">
   <si>
     <t>球員中文名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1715,12 +1715,273 @@
     <t>韓國</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>荷西·阿爾瓦拉多</t>
+  </si>
+  <si>
+    <t>埃杜亞德·巴札多</t>
+  </si>
+  <si>
+    <t>荷西·布托</t>
+  </si>
+  <si>
+    <t>恩曼紐爾·德·傑蘇斯</t>
+  </si>
+  <si>
+    <t>約恩德里斯·戈麥斯</t>
+  </si>
+  <si>
+    <t>卡洛斯·古茲曼</t>
+  </si>
+  <si>
+    <t>安德烈斯·馬查多</t>
+  </si>
+  <si>
+    <t>赫曼·馬奎茲</t>
+  </si>
+  <si>
+    <t>凱德·蒙特羅</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF151F28"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>歐達尼爾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF151F28"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF151F28"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>瑪斯奎達</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF151F28"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>丹尼爾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF151F28"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF151F28"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>帕倫西亞</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛德華多·羅德里奎茲</t>
+  </si>
+  <si>
+    <t>里卡多·桑切斯</t>
+  </si>
+  <si>
+    <t>安東尼歐·森薩泰拉</t>
+  </si>
+  <si>
+    <t>藍傑·蘇亞瑞茲</t>
+  </si>
+  <si>
+    <t>安海爾·澤帕</t>
+  </si>
+  <si>
+    <t>威廉·康崔拉斯</t>
+  </si>
+  <si>
+    <t>薩爾瓦多·培瑞茲</t>
+  </si>
+  <si>
+    <t>路易斯·厄萊茲</t>
+  </si>
+  <si>
+    <t>威爾遜·康崔拉斯</t>
+  </si>
+  <si>
+    <t>麥凱爾·賈西亞</t>
+  </si>
+  <si>
+    <t>安德列斯·席曼尼茲</t>
+  </si>
+  <si>
+    <t>埃尤亨尼歐·蘇亞瑞茲</t>
+  </si>
+  <si>
+    <t>葛雷伯·托雷斯</t>
+  </si>
+  <si>
+    <t>伊茲基爾·托瓦</t>
+  </si>
+  <si>
+    <t>威爾耶·阿布瑞尤</t>
+  </si>
+  <si>
+    <t>小羅納德·阿庫尼亞</t>
+  </si>
+  <si>
+    <t>傑克森·喬里奧</t>
+  </si>
+  <si>
+    <t>哈維爾·薩諾哈</t>
+  </si>
+  <si>
+    <t>Jose Alvarado</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eduard Bazardo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jose Butto</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enmanuel De Jesus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yoendrys Gomez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carlos Guzman</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Andres Machado</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>German Marquez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oddanier Mosqueda</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daniel Palencia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ricardo Sanchez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antonio Senzatela</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Angel Zerpa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>William Contreras</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salvador Perez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luis Arraez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Willson Contreras</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maikel Garcia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Andres Gimenez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eugenio Suarez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gleyber Torres</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ezequiel Tovar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wilyer Abreu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ronald Acuna Jr.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jackson Chourio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Javier Sanoja</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1767,8 +2028,41 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF151F28"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF151F28"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF151F28"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF151F28"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF151F28"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1778,6 +2072,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1811,7 +2111,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1832,6 +2132,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2147,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C309DF4F-2503-4A7A-8142-F5EFFBD43B16}">
-  <dimension ref="A1:C184"/>
+  <dimension ref="A1:C213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
@@ -4177,6 +4489,238 @@
       </c>
       <c r="C184" s="2" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A185" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A186" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A187" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A188" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A189" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A190" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A191" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A192" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A193" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A194" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A195" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A196" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A197" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A198" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A199" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A200" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A201" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A202" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A203" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A204" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A205" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A206" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A207" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A208" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A209" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A210" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A211" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A212" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A213" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/球員中英文對照（更新）.xlsx
+++ b/球員中英文對照（更新）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Desktop/NTU/灼見/python-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412897FD-D14C-F844-9B91-6B500FE82241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E57373F-D029-7B4E-BF17-90C905BB574D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="432">
   <si>
     <t>球員中文名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1714,33 +1714,6 @@
   <si>
     <t>韓國</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>荷西·阿爾瓦拉多</t>
-  </si>
-  <si>
-    <t>埃杜亞德·巴札多</t>
-  </si>
-  <si>
-    <t>荷西·布托</t>
-  </si>
-  <si>
-    <t>恩曼紐爾·德·傑蘇斯</t>
-  </si>
-  <si>
-    <t>約恩德里斯·戈麥斯</t>
-  </si>
-  <si>
-    <t>卡洛斯·古茲曼</t>
-  </si>
-  <si>
-    <t>安德烈斯·馬查多</t>
-  </si>
-  <si>
-    <t>赫曼·馬奎茲</t>
-  </si>
-  <si>
-    <t>凱德·蒙特羅</t>
   </si>
   <si>
     <r>
@@ -1807,173 +1780,231 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Jose Alvarado</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eduard Bazardo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jose Butto</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enmanuel De Jesus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yoendrys Gomez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carlos Guzman</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Andres Machado</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>German Marquez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oddanier Mosqueda</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daniel Palencia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ricardo Sanchez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antonio Senzatela</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Angel Zerpa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>William Contreras</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salvador Perez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luis Arraez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Willson Contreras</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maikel Garcia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Andres Gimenez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eugenio Suarez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gleyber Torres</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ezequiel Tovar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wilyer Abreu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ronald Acuna Jr.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jackson Chourio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Javier Sanoja</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>荷西·阿爾瓦拉多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>埃杜亞德·巴札多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>荷西·布托</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恩曼紐爾·德·傑蘇斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>約恩德里斯·戈麥斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡洛斯·古茲曼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>安德烈斯·馬查多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>赫曼·馬奎茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凱德·蒙特羅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>愛德華多·羅德里奎茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>里卡多·桑切斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>安東尼歐·森薩泰拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>藍傑·蘇亞瑞茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>安海爾·澤帕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>威廉·康崔拉斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>薩爾瓦多·培瑞茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>路易斯·厄萊茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>威爾遜·康崔拉斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>麥凱爾·賈西亞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>安德列斯·席曼尼茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>埃尤亨尼歐·蘇亞瑞茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>葛雷伯·托雷斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>伊茲基爾·托瓦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>威爾耶·阿布瑞尤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>小羅納德·阿庫尼亞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>傑克森·喬里奧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>哈維爾·薩諾哈</t>
-  </si>
-  <si>
-    <t>Jose Alvarado</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eduard Bazardo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jose Butto</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enmanuel De Jesus</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yoendrys Gomez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carlos Guzman</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Andres Machado</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>German Marquez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Oddanier Mosqueda</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Daniel Palencia</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ricardo Sanchez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Antonio Senzatela</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Angel Zerpa</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>William Contreras</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Salvador Perez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Luis Arraez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Willson Contreras</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maikel Garcia</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Andres Gimenez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eugenio Suarez</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gleyber Torres</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ezequiel Tovar</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wilyer Abreu</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ronald Acuna Jr.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jackson Chourio</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Javier Sanoja</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>委內瑞拉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1981,7 +2012,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2044,25 +2075,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF151F28"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF151F28"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF151F28"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2072,12 +2090,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2111,7 +2123,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2132,18 +2144,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4492,235 +4492,238 @@
       </c>
     </row>
     <row r="185" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A185" s="7" t="s">
+      <c r="A185" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A186" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A187" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A188" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A189" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A190" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A191" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A192" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A193" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A194" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="B185" s="10" t="s">
+      <c r="B194" s="6" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A195" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A196" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A197" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A198" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A199" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A200" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A201" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A202" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A203" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A204" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A205" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A206" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A207" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A208" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A209" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A210" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A211" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A212" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B212" s="6" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A186" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="B186" s="10" t="s">
+    <row r="213" spans="1:2" ht="21.5" customHeight="1">
+      <c r="A213" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B213" s="6" t="s">
         <v>403</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A187" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="B187" s="10" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A188" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="B188" s="10" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A189" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="B189" s="10" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A190" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="B190" s="10" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A191" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="B191" s="10" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A192" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="B192" s="10" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A193" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="B193" s="10" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A194" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B194" s="10" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A195" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="B195" s="10" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A196" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="B196" s="10" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A197" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="B197" s="10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A198" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="B198" s="10" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A199" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="B199" s="10" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A200" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="B200" s="10" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A201" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="B201" s="10" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A202" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="B202" s="10" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A203" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="B203" s="10" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A204" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="B204" s="10" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A205" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="B205" s="10" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A206" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="B206" s="10" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A207" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="B207" s="10" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A208" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A209" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B209" s="10" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A210" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A211" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="B211" s="10" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A212" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="B212" s="10" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A213" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="B213" s="10" t="s">
-        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/球員中英文對照（更新）.xlsx
+++ b/球員中英文對照（更新）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Desktop/NTU/灼見/python-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E57373F-D029-7B4E-BF17-90C905BB574D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6019917A-96C6-AF46-867E-1E07504A88F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="432">
   <si>
     <t>球員中文名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4558,7 +4558,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="21.5" customHeight="1">
+    <row r="193" spans="1:3" ht="21.5" customHeight="1">
       <c r="A193" s="6" t="s">
         <v>412</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="21.5" customHeight="1">
+    <row r="194" spans="1:3" ht="21.5" customHeight="1">
       <c r="A194" s="6" t="s">
         <v>373</v>
       </c>
@@ -4574,15 +4574,18 @@
         <v>384</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="21.5" customHeight="1">
+    <row r="195" spans="1:3" ht="21.5" customHeight="1">
       <c r="A195" s="6" t="s">
         <v>374</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="196" spans="1:2" ht="21.5" customHeight="1">
+      <c r="C195" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="21.5" customHeight="1">
       <c r="A196" s="6" t="s">
         <v>413</v>
       </c>
@@ -4590,7 +4593,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="21.5" customHeight="1">
+    <row r="197" spans="1:3" ht="21.5" customHeight="1">
       <c r="A197" s="6" t="s">
         <v>414</v>
       </c>
@@ -4598,7 +4601,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="21.5" customHeight="1">
+    <row r="198" spans="1:3" ht="21.5" customHeight="1">
       <c r="A198" s="6" t="s">
         <v>415</v>
       </c>
@@ -4606,7 +4609,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="21.5" customHeight="1">
+    <row r="199" spans="1:3" ht="21.5" customHeight="1">
       <c r="A199" s="6" t="s">
         <v>416</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="21.5" customHeight="1">
+    <row r="200" spans="1:3" ht="21.5" customHeight="1">
       <c r="A200" s="6" t="s">
         <v>417</v>
       </c>
@@ -4622,7 +4625,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="21.5" customHeight="1">
+    <row r="201" spans="1:3" ht="21.5" customHeight="1">
       <c r="A201" s="6" t="s">
         <v>418</v>
       </c>
@@ -4630,7 +4633,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="21.5" customHeight="1">
+    <row r="202" spans="1:3" ht="21.5" customHeight="1">
       <c r="A202" s="6" t="s">
         <v>419</v>
       </c>
@@ -4638,7 +4641,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="21.5" customHeight="1">
+    <row r="203" spans="1:3" ht="21.5" customHeight="1">
       <c r="A203" s="6" t="s">
         <v>420</v>
       </c>
@@ -4646,7 +4649,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="21.5" customHeight="1">
+    <row r="204" spans="1:3" ht="21.5" customHeight="1">
       <c r="A204" s="6" t="s">
         <v>421</v>
       </c>
@@ -4654,7 +4657,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="21.5" customHeight="1">
+    <row r="205" spans="1:3" ht="21.5" customHeight="1">
       <c r="A205" s="6" t="s">
         <v>422</v>
       </c>
@@ -4662,7 +4665,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="21.5" customHeight="1">
+    <row r="206" spans="1:3" ht="21.5" customHeight="1">
       <c r="A206" s="6" t="s">
         <v>423</v>
       </c>
@@ -4670,7 +4673,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="21.5" customHeight="1">
+    <row r="207" spans="1:3" ht="21.5" customHeight="1">
       <c r="A207" s="6" t="s">
         <v>424</v>
       </c>
@@ -4678,7 +4681,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="21.5" customHeight="1">
+    <row r="208" spans="1:3" ht="21.5" customHeight="1">
       <c r="A208" s="6" t="s">
         <v>425</v>
       </c>

--- a/球員中英文對照（更新）.xlsx
+++ b/球員中英文對照（更新）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Desktop/NTU/灼見/python-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6019917A-96C6-AF46-867E-1E07504A88F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0D8E4F-8203-8E45-9633-DFEEF2B93017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="493">
   <si>
     <t>球員中文名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2005,6 +2005,250 @@
   </si>
   <si>
     <t>委內瑞拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Albert Abreu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>多明尼加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elvis Alvarado</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brayan Bello</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huascar Brazoban</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seranthony Dominguez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Camilo Doval</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carlos Estevez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wandy Peralta</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cristopher Sanchez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dennis Santana</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luis Severino</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gregory Soto</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edwin Uceta</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abner Uribe</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agustin Ramirez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Austin Wells</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Junior Caminero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vladimir Guerrero Jr.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manny Machado</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ketel Marte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jeremy Pena</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Geraldo Perdomo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amed Rosario</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carlos Santana</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡洛斯 桑塔納</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oneil Cruz</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歐尼爾·克魯茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Julio Rodriguez</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Johan Rojas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>約翰 羅哈斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Juan Soto</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡安·索托</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fernando Tatis Jr.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小費南多 塔提斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>亞伯特·阿布瑞尤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>山迪·艾爾康塔拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾維斯·阿爾瓦拉多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉楊·貝約</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>華斯卡·布拉佐萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑟蘭東尼·多明格茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡米洛·多瓦爾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡洛斯·埃斯泰維茲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>汪迪·培洛塔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>克里斯多福·桑契斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丹尼斯·桑塔納</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>路易斯·塞佛里諾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>葛瑞戈里·索托</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>埃德溫·烏塞塔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾卜納·烏里貝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿古斯丁·拉米雷斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奧斯汀·威爾斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>朱尼爾·卡米內羅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小弗拉迪米爾·葛雷諾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>曼尼·馬查多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凱特爾·馬提</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>傑瑞米·佩尼亞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>赫拉多·珀多莫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾梅德·羅薩里奧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡立歐·羅德里奎茲</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2459,7 +2703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C309DF4F-2503-4A7A-8142-F5EFFBD43B16}">
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C243"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
@@ -4492,241 +4736,652 @@
       </c>
     </row>
     <row r="185" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A185" s="6" t="s">
+      <c r="A185" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A186" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A187" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A188" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A189" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A190" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A191" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A192" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A193" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A194" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A195" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A196" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A197" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A198" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A199" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A200" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A201" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A202" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A203" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A204" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A205" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A206" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A208" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A209" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A210" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A211" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A212" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A213" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A214" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A215" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B185" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="C185" s="2" t="s">
+      <c r="C215" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A186" s="6" t="s">
+    <row r="216" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A216" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B186" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A187" s="6" t="s">
+      <c r="C216" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A217" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B187" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A188" s="6" t="s">
+      <c r="C217" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A218" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="6" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A189" s="6" t="s">
+      <c r="C218" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A219" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B189" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A190" s="6" t="s">
+      <c r="C219" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A220" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B190" s="6" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A191" s="6" t="s">
+      <c r="C220" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A221" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B191" s="6" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A192" s="6" t="s">
+      <c r="C221" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A222" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B192" s="6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A193" s="6" t="s">
+      <c r="C222" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A223" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B193" s="6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A194" s="6" t="s">
+      <c r="C223" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A224" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B194" s="6" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A195" s="6" t="s">
+      <c r="C224" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A225" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B195" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="C195" s="2" t="s">
+      <c r="C225" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A196" s="6" t="s">
+    <row r="226" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A226" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B196" s="6" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A197" s="6" t="s">
+      <c r="C226" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A227" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B197" s="6" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A198" s="6" t="s">
+      <c r="C227" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A228" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B198" s="6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A199" s="6" t="s">
+      <c r="C228" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A229" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B199" s="6" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A200" s="6" t="s">
+      <c r="C229" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A230" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B200" s="6" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A201" s="6" t="s">
+      <c r="C230" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A231" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B201" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A202" s="6" t="s">
+      <c r="C231" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A232" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B202" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A203" s="6" t="s">
+      <c r="C232" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A233" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B203" s="6" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A204" s="6" t="s">
+      <c r="C233" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A234" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B204" s="6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A205" s="6" t="s">
+      <c r="C234" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A235" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B205" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A206" s="6" t="s">
+      <c r="C235" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A236" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B206" s="6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A207" s="6" t="s">
+      <c r="C236" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A237" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B207" s="6" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="21.5" customHeight="1">
-      <c r="A208" s="6" t="s">
+      <c r="C237" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A238" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B208" s="6" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A209" s="6" t="s">
+      <c r="C238" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A239" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B209" s="6" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A210" s="6" t="s">
+      <c r="C239" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A240" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B210" s="6" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A211" s="6" t="s">
+      <c r="C240" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A241" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B211" s="6" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A212" s="6" t="s">
+      <c r="C241" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A242" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B212" s="6" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" ht="21.5" customHeight="1">
-      <c r="A213" s="6" t="s">
+      <c r="C242" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A243" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B213" s="6" t="s">
-        <v>403</v>
+      <c r="C243" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/球員中英文對照（更新）.xlsx
+++ b/球員中英文對照（更新）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Desktop/NTU/灼見/python-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0D8E4F-8203-8E45-9633-DFEEF2B93017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3978F9-B09A-A241-AC75-F1A68696DF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
   </bookViews>
@@ -2703,7 +2703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C309DF4F-2503-4A7A-8142-F5EFFBD43B16}">
-  <dimension ref="A1:C243"/>
+  <dimension ref="A1:G243"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
@@ -4647,7 +4647,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="21.5" customHeight="1">
+    <row r="177" spans="1:7" ht="21.5" customHeight="1">
       <c r="A177" s="6" t="s">
         <v>352</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="21.5" customHeight="1">
+    <row r="178" spans="1:7" ht="21.5" customHeight="1">
       <c r="A178" s="6" t="s">
         <v>354</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="21.5" customHeight="1">
+    <row r="179" spans="1:7" ht="21.5" customHeight="1">
       <c r="A179" s="6" t="s">
         <v>356</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="21.5" customHeight="1">
+    <row r="180" spans="1:7" ht="21.5" customHeight="1">
       <c r="A180" s="6" t="s">
         <v>358</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="21.5" customHeight="1">
+    <row r="181" spans="1:7" ht="21.5" customHeight="1">
       <c r="A181" s="1" t="s">
         <v>360</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="21.5" customHeight="1">
+    <row r="182" spans="1:7" ht="21.5" customHeight="1">
       <c r="A182" s="1" t="s">
         <v>362</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="21.5" customHeight="1">
+    <row r="183" spans="1:7" ht="21.5" customHeight="1">
       <c r="A183" s="1" t="s">
         <v>364</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="21.5" customHeight="1">
+    <row r="184" spans="1:7" ht="21.5" customHeight="1">
       <c r="A184" s="1" t="s">
         <v>366</v>
       </c>
@@ -4735,654 +4735,713 @@
         <v>372</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="21.5" customHeight="1">
+    <row r="185" spans="1:7" ht="21.5" customHeight="1">
       <c r="A185" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G185" s="1"/>
+    </row>
+    <row r="186" spans="1:7" ht="21.5" customHeight="1">
       <c r="A186" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G186" s="1"/>
+    </row>
+    <row r="187" spans="1:7" ht="21.5" customHeight="1">
       <c r="A187" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G187" s="1"/>
+    </row>
+    <row r="188" spans="1:7" ht="21.5" customHeight="1">
       <c r="A188" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G188" s="1"/>
+    </row>
+    <row r="189" spans="1:7" ht="21.5" customHeight="1">
       <c r="A189" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>472</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G189" s="1"/>
+    </row>
+    <row r="190" spans="1:7" ht="21.5" customHeight="1">
       <c r="A190" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G190" s="1"/>
+    </row>
+    <row r="191" spans="1:7" ht="21.5" customHeight="1">
       <c r="A191" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G191" s="1"/>
+    </row>
+    <row r="192" spans="1:7" ht="21.5" customHeight="1">
       <c r="A192" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G192" s="1"/>
+    </row>
+    <row r="193" spans="1:7" ht="21.5" customHeight="1">
       <c r="A193" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G193" s="1"/>
+    </row>
+    <row r="194" spans="1:7" ht="21.5" customHeight="1">
       <c r="A194" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G194" s="1"/>
+    </row>
+    <row r="195" spans="1:7" ht="21.5" customHeight="1">
       <c r="A195" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G195" s="1"/>
+    </row>
+    <row r="196" spans="1:7" ht="21.5" customHeight="1">
       <c r="A196" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G196" s="1"/>
+    </row>
+    <row r="197" spans="1:7" ht="21.5" customHeight="1">
       <c r="A197" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G197" s="1"/>
+    </row>
+    <row r="198" spans="1:7" ht="21.5" customHeight="1">
       <c r="A198" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G198" s="1"/>
+    </row>
+    <row r="199" spans="1:7" ht="21.5" customHeight="1">
       <c r="A199" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G199" s="1"/>
+    </row>
+    <row r="200" spans="1:7" ht="21.5" customHeight="1">
       <c r="A200" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G200" s="1"/>
+    </row>
+    <row r="201" spans="1:7" ht="21.5" customHeight="1">
       <c r="A201" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G201" s="1"/>
+    </row>
+    <row r="202" spans="1:7" ht="21.5" customHeight="1">
       <c r="A202" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G202" s="1"/>
+    </row>
+    <row r="203" spans="1:7" ht="21.5" customHeight="1">
       <c r="A203" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G203" s="1"/>
+    </row>
+    <row r="204" spans="1:7" ht="21.5" customHeight="1">
       <c r="A204" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G204" s="1"/>
+    </row>
+    <row r="205" spans="1:7" ht="21.5" customHeight="1">
       <c r="A205" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G205" s="1"/>
+    </row>
+    <row r="206" spans="1:7" ht="21.5" customHeight="1">
       <c r="A206" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G206" s="1"/>
+    </row>
+    <row r="207" spans="1:7" ht="21.5" customHeight="1">
       <c r="A207" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G207" s="1"/>
+    </row>
+    <row r="208" spans="1:7" ht="21.5" customHeight="1">
       <c r="A208" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G208" s="1"/>
+    </row>
+    <row r="209" spans="1:7" ht="21.5" customHeight="1">
       <c r="A209" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G209" s="1"/>
+    </row>
+    <row r="210" spans="1:7" ht="21.5" customHeight="1">
       <c r="A210" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G210" s="1"/>
+    </row>
+    <row r="211" spans="1:7" ht="21.5" customHeight="1">
       <c r="A211" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G211" s="1"/>
+    </row>
+    <row r="212" spans="1:7" ht="21.5" customHeight="1">
       <c r="A212" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G212" s="1"/>
+    </row>
+    <row r="213" spans="1:7" ht="21.5" customHeight="1">
       <c r="A213" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G213" s="1"/>
+    </row>
+    <row r="214" spans="1:7" ht="21.5" customHeight="1">
       <c r="A214" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G214" s="1"/>
+    </row>
+    <row r="215" spans="1:7" ht="21.5" customHeight="1">
       <c r="A215" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G215" s="1"/>
+    </row>
+    <row r="216" spans="1:7" ht="21.5" customHeight="1">
       <c r="A216" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G216" s="1"/>
+    </row>
+    <row r="217" spans="1:7" ht="21.5" customHeight="1">
       <c r="A217" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G217" s="1"/>
+    </row>
+    <row r="218" spans="1:7" ht="21.5" customHeight="1">
       <c r="A218" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G218" s="1"/>
+    </row>
+    <row r="219" spans="1:7" ht="21.5" customHeight="1">
       <c r="A219" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>408</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G219" s="1"/>
+    </row>
+    <row r="220" spans="1:7" ht="21.5" customHeight="1">
       <c r="A220" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G220" s="1"/>
+    </row>
+    <row r="221" spans="1:7" ht="21.5" customHeight="1">
       <c r="A221" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G221" s="1"/>
+    </row>
+    <row r="222" spans="1:7" ht="21.5" customHeight="1">
       <c r="A222" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G222" s="1"/>
+    </row>
+    <row r="223" spans="1:7" ht="21.5" customHeight="1">
       <c r="A223" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G223" s="1"/>
+    </row>
+    <row r="224" spans="1:7" ht="21.5" customHeight="1">
       <c r="A224" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G224" s="1"/>
+    </row>
+    <row r="225" spans="1:7" ht="21.5" customHeight="1">
       <c r="A225" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G225" s="1"/>
+    </row>
+    <row r="226" spans="1:7" ht="21.5" customHeight="1">
       <c r="A226" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G226" s="1"/>
+    </row>
+    <row r="227" spans="1:7" ht="21.5" customHeight="1">
       <c r="A227" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G227" s="1"/>
+    </row>
+    <row r="228" spans="1:7" ht="21.5" customHeight="1">
       <c r="A228" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G228" s="1"/>
+    </row>
+    <row r="229" spans="1:7" ht="21.5" customHeight="1">
       <c r="A229" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G229" s="1"/>
+    </row>
+    <row r="230" spans="1:7" ht="21.5" customHeight="1">
       <c r="A230" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G230" s="1"/>
+    </row>
+    <row r="231" spans="1:7" ht="21.5" customHeight="1">
       <c r="A231" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G231" s="1"/>
+    </row>
+    <row r="232" spans="1:7" ht="21.5" customHeight="1">
       <c r="A232" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G232" s="1"/>
+    </row>
+    <row r="233" spans="1:7" ht="21.5" customHeight="1">
       <c r="A233" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G233" s="1"/>
+    </row>
+    <row r="234" spans="1:7" ht="21.5" customHeight="1">
       <c r="A234" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G234" s="1"/>
+    </row>
+    <row r="235" spans="1:7" ht="21.5" customHeight="1">
       <c r="A235" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G235" s="1"/>
+    </row>
+    <row r="236" spans="1:7" ht="21.5" customHeight="1">
       <c r="A236" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G236" s="1"/>
+    </row>
+    <row r="237" spans="1:7" ht="21.5" customHeight="1">
       <c r="A237" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G237" s="1"/>
+    </row>
+    <row r="238" spans="1:7" ht="21.5" customHeight="1">
       <c r="A238" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G238" s="1"/>
+    </row>
+    <row r="239" spans="1:7" ht="21.5" customHeight="1">
       <c r="A239" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G239" s="1"/>
+    </row>
+    <row r="240" spans="1:7" ht="21.5" customHeight="1">
       <c r="A240" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G240" s="1"/>
+    </row>
+    <row r="241" spans="1:7" ht="21.5" customHeight="1">
       <c r="A241" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G241" s="1"/>
+    </row>
+    <row r="242" spans="1:7" ht="21.5" customHeight="1">
       <c r="A242" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" ht="21.5" customHeight="1">
+      <c r="G242" s="1"/>
+    </row>
+    <row r="243" spans="1:7" ht="21.5" customHeight="1">
       <c r="A243" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>431</v>
       </c>
+      <c r="G243" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C46" xr:uid="{C309DF4F-2503-4A7A-8142-F5EFFBD43B16}">

--- a/球員中英文對照（更新）.xlsx
+++ b/球員中英文對照（更新）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caizhengying/Desktop/NTU/灼見/python-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3978F9-B09A-A241-AC75-F1A68696DF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A2D760-F48D-E344-B00E-F62F9B53196C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A0F935E1-CD91-442B-8410-645DC1865189}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="495">
   <si>
     <t>球員中文名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2250,6 +2250,12 @@
   <si>
     <t>胡立歐·羅德里奎茲</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>路易斯·卡斯提歐</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
   </si>
 </sst>
 </file>
@@ -2703,7 +2709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C309DF4F-2503-4A7A-8142-F5EFFBD43B16}">
-  <dimension ref="A1:G243"/>
+  <dimension ref="A1:G244"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
@@ -5442,6 +5448,17 @@
         <v>431</v>
       </c>
       <c r="G243" s="1"/>
+    </row>
+    <row r="244" spans="1:7" ht="21.5" customHeight="1">
+      <c r="A244" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>433</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C46" xr:uid="{C309DF4F-2503-4A7A-8142-F5EFFBD43B16}">
